--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,446 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dennis-et-al-2026-recommendations-in-extracorporeal-cardiopulmonary-resuscitation-post-resuscitation-care-via-an.json</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582026001408-main.json</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:00:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>acc-003425.json</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:04:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>diagnostic_and_prognostic_value_of_the_venous.875.json</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:06:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>jcm-15-04227.json</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:07:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>jcm-15-04453.json</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PIIS2772930324000681.json</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>38</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PIIS2950133426001102.json</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:11:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>s10741-026-10636-0.json</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>s10877-026-01457-5.json</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>s40001-026-04401-0.json</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>58</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2772963X26002577-main.json</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>59</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>magnesium_sulfate_to_prevent_perioperative_atrial.847.json</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>62</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>s12245-025-01078-w.json</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:22:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>evidence_based,_cost_effective_management_of_lower.1388.json</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>71</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:25:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2667100X26000320-main.json</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>78</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:27:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>evidence_based,_cost_effective_management_of_upper.3.json</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:29:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UEG Journal - 2026 - Cárdenas‐Jaén - AEG‐AESPANC‐OPGE‐SIED‐SPG Ibero‐Latin American Guidelines on Acute Pancreatitis .json</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>90</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:32:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PIIS103673142600041X.json</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>95</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:33:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>blood_bld-2023-022899-c-main.json</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>103</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1-s2.0-S1665268124005349-main.json</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>108</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chronic-hepatitis-B-in-2025--diagnosis--treatment-and-fut_2025_Clinical-Medi.json</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>117</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:16:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,926 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adedinsewo-et-al-2026-heart-failure-occurring-in-the-perinatal-period-a-scientific-statement-from-the-american-heart.json</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>124</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:45:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ruel-et-al-2026-secondary-prevention-after-coronary-artery-bypass-graft-surgery-2026-update-a-scientific-statement-from.json</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>133</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:50:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PIIS0007091226003296.json</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>139</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:52:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Left ventricular outflow tract obstruction in critically ill patients.json</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>149</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:54:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>medicina-62-01070 (1).json</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>154</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>medicina-62-01070.json</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>164</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:00:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>association_between_acute_gastrointestinal_injury.7.json</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>171</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PIIS0007091226002734.json</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>179</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:04:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>diagnostics-16-01548.json</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>191</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:07:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gut_microbiome_brain_cirrhosis_axis.19.json</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>204</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hepatitis-C--current-treatments--emerging-therapies-and-tackli_2025_Clinical.json</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>213</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hepatocellular-carcinoma--HCC---An-update-on-risk-factors--su_2025_Clinical-.json</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>222</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Management-of-acute-decompensated-cirrhosis_2025_Clinical-Medicine.json</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>244</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Metabolic-dysfunction-associated-steatotic-liver-disea_2025_Clinical-Medicin.json</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>251</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Palliative-care-in-advanced-liver-disease_2025_Clinical-Medicine.json</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>262</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:21:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fmed-13-1808427.json</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>271</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:23:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>s13054-026-06142-2_reference.json</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>278</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582025020321-main.json</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>285</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:27:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>creager-et-al-2026-2026-aha-acc-accp-acep-chest-scai-shm-sir-svm-svn-guideline-for-the-evaluation-and-management-of.json</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>293</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:31:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bmj-2025-084675.full.json</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>311</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:34:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>s13054-026-06144-0.json</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>319</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:36:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>s13054-023-04632-1.json</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>328</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:38:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2772529426000470.json</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>336</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:41:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>prabhakaran-et-al-2026-2026-guideline-for-the-early-management-of-patients-with-acute-ischemic-stroke-a-guideline-from.json</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>344</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:45:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>current_management_of_traumatic_intracranial.1.json</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>356</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:46:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fmed-13-1775538.json</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>365</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:51:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ketamine for status epilepticus.json</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>376</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:53:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>nutrients-18-01359.json</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>384</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:54:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>s12028-023-01752-y (1).json</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>395</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:58:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>s12028-026-02551-x.json</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>402</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:00:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>s12028-026-02565-5.json</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>408</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:01:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025_elso_consensus_statement_for_the_provision.2.json</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>418</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nutrition in ICU.json</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>428</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:07:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Acute-confusion-in-pregnancy_2025_Clinical-Medicine.json</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>443</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:09:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Approach-to-investigation-and-management-of-proteinuria-i_2025_Clinical-Medi.json</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>457</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Severe-acute-pulmonary-embolism-in-pregnancy_2025_Clinical-Medicine.json</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>468</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:14:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ti-39-16284.json</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>476</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:17:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2965-2774-ccsci-38-e20260215.json</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>484</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fmed-13-1857404.json</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>490</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:21:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>life-16-00913.json</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>497</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:24:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>s00134-026-08491-6.json</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>508</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>s13054-026-06075-w.json</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>518</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:30:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>the_vicious_cycle__delirium,_sedation,_and_patient.7.json</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>530</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:34:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fendo-15-1473151.json</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>538</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:37:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>000549732.json</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>545</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:40:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582025020199-main.json</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>555</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:43:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1838,106 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>rccm.202507-1692st.json</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>561</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:46:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PIIS0007091225009353.json</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>571</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>s13054-026-06075-w.pdf.xml.json</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>577</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>The effects of asymmetrical versus symmetrical high-flow nasal cannula on respiratory muscle activity in acute hypoxaemic respiratory failure and chro.json</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>583</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:54:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1-s2.0-S1470211824054629.json</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>591</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:57:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1938,6 +1938,146 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582026000658-main.json</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>601</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:59:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>a-2725-7350.json</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>611</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:01:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>advances_in_achieving_lung_and.7.json</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>620</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:03:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fimmu-14-1230049.json</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>631</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Flexible-bronchoscopy-in-.json</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>646</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>jcm-14-02067.json</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>656</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:11:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>neurolint-18-00085-v2.json</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>665</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:13:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2078,6 +2078,86 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>pathophysiology-33-00036.json</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>683</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:17:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>s00134-026-08496-1.json</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>693</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:19:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>s00134-026-08503-5.json</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>700</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>s13054-026-06111-9.json</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>706</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:22:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,6 +2158,46 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>s00134-026-08459-6.json</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>711</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>surviving_sepsis_campaign__international.5 (1).json</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>723</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:27:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pearls_processed.xlsx
+++ b/pearls_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2198,286 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>surviving_sepsis_campaign__international.5.json</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>733</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:31:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>dexmedetomidine_versus_usual_care_in_adult.10.json</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>736</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:32:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2667100X26001180-main.json</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>742</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>acc-000884.json</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>754</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>rapid_microbiological_diagnostics_for_sepsis_.6.json</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>762</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:37:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>s15010-026-02852-5.json</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>772</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:39:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>WJCCM-15-114264.json</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>783</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:42:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>howard-quijano-et-al-2026-perioperative-anemia-and-patient-blood-management-in-cardiac-surgery-a-scientific-statement.json</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>793</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:44:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1-s2.0-S0022480426003471.json</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>801</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:47:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2352556826001219-main.json</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>807</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:49:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>s00330-026-12440-8.json</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>816</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:51:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>s00508-026-02771-3.json</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>826</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>e001369.full.json</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>836</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:56:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>prophylaxis_of_venous_thromboembolism_in_trauma_.2.json</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>849</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:59:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
